--- a/results/reliability_eval/Llama-3-8B_P1376_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P1376_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5797233325452635</v>
+        <v>0.6431210306659408</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8184125010643337</v>
+        <v>0.2621257496298508</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5795034061106561</v>
+        <v>0.6431645799310471</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8182377613758646</v>
+        <v>0.2621257496298508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4190945628687204</v>
+        <v>0.3626710215931773</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7268062088406571</v>
+        <v>0.1377607017082078</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9971162146262075</v>
+        <v>0.9866993286154964</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9988275071371554</v>
+        <v>0.9286940189934842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.761</v>
+        <v>0.165</v>
       </c>
     </row>
   </sheetData>
